--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Мариуполь 130439503.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Мариуполь 130439503.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC7DD82-34F4-44F2-840A-2A2B15CDB264}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1C4961-E92B-47CC-88E9-0F13992F6F63}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -172,6 +172,27 @@
   <si>
     <t>ООО "НОВОЕ ВРЕМЯ" Мариуполь</t>
   </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм кор.0.5кг зам_NEW</t>
+  </si>
+  <si>
+    <t>С КАРТОФ.И ГРИБ.вареники пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм пл. 0.7кг 10шт.зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ ПРЕМИУМ пельм кор.0.4кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм 4кг зам.</t>
+  </si>
 </sst>
 </file>
 
@@ -299,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,20 +368,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="lightHorizontal">
-        <fgColor indexed="42"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -550,30 +559,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="57"/>
-      </left>
-      <right style="double">
-        <color indexed="57"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -583,7 +568,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -732,22 +717,10 @@
     <xf numFmtId="1" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -755,12 +728,6 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -782,48 +749,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1243,14 +1169,14 @@
         <f>K5</f>
         <v>130439503</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="64"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1283,23 +1209,23 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="52">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="55">
+      <c r="F3" s="52">
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="65" t="str">
+      <c r="G3" s="59" t="str">
         <f>L5</f>
         <v>ООО "НОВОЕ ВРЕМЯ" Мариуполь</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="67"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1435,7 +1361,8 @@
       <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56">
+      <c r="A12" s="53" t="str">
+        <f>RIGHT(D12,4)</f>
         <v>5897</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -1464,7 +1391,8 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
+      <c r="A13" s="53" t="str">
+        <f t="shared" ref="A13:A30" si="0">RIGHT(D13,4)</f>
         <v>6149</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -1481,7 +1409,7 @@
         <v>0.3</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" ref="G13:G19" si="0">E13*F13</f>
+        <f t="shared" ref="G13:G19" si="1">E13*F13</f>
         <v>0</v>
       </c>
       <c r="H13" s="14">
@@ -1493,7 +1421,8 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
+      <c r="A14" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6819</v>
       </c>
       <c r="B14" s="48" t="s">
@@ -1510,7 +1439,7 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
@@ -1522,7 +1451,8 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56">
+      <c r="A15" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6202</v>
       </c>
       <c r="B15" s="48" t="s">
@@ -1539,7 +1469,7 @@
         <v>0.3</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H15" s="14">
@@ -1551,7 +1481,8 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
+      <c r="A16" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6148</v>
       </c>
       <c r="B16" s="48" t="s">
@@ -1568,7 +1499,7 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="14">
@@ -1580,7 +1511,8 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56">
+      <c r="A17" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6209</v>
       </c>
       <c r="B17" s="48" t="s">
@@ -1597,7 +1529,7 @@
         <v>0.35</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -1609,7 +1541,8 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56">
+      <c r="A18" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6168</v>
       </c>
       <c r="B18" s="48" t="s">
@@ -1626,7 +1559,7 @@
         <v>0.35</v>
       </c>
       <c r="G18" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" s="14">
@@ -1638,7 +1571,8 @@
       <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56">
+      <c r="A19" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5579</v>
       </c>
       <c r="B19" s="48" t="s">
@@ -1655,7 +1589,7 @@
         <v>0.42</v>
       </c>
       <c r="G19" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="14">
@@ -1667,10 +1601,11 @@
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57">
+      <c r="A20" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5754</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="54" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="46" t="s">
@@ -1683,7 +1618,7 @@
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G20" s="55">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1696,7 +1631,8 @@
       <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57">
+      <c r="A21" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5755</v>
       </c>
       <c r="B21" s="48" t="s">
@@ -1712,7 +1648,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G21" s="55">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1724,136 +1660,249 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60">
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>7216</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="54" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="47">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="53"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="55">
         <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
-      <c r="B24" s="43" t="s">
+      <c r="I23" s="14"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>6824</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="47">
+        <v>1002112606824</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="55">
+        <f t="shared" ref="G24:G29" si="2">E24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7049</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="47">
+        <v>1002151787049</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G25" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7085</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="47">
+        <v>1002112607085</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G26" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7212</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="47">
+        <v>1002112857212</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G27" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7214</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="47">
+        <v>1002112857214</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G28" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7224</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="47">
+        <v>1002116517224</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7375</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="47">
+        <v>1002112857375</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="22">
+        <v>1</v>
+      </c>
+      <c r="G30" s="55">
+        <f>E30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="49"/>
+      <c r="B31" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="16">
-        <f>SUM(E10:E23)</f>
+      <c r="C31" s="15"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="16">
+        <f>SUM(E10:E30)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16">
-        <f>SUM(G12:G23)</f>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16">
+        <f>SUM(G10:G30)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="35"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="38"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="35"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="38"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="38"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="35"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="38"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="35"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="38"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="35"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="38"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="38"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B32" s="35"/>
       <c r="C32" s="17"/>
       <c r="D32" s="38"/>
@@ -16930,16 +16979,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
